--- a/data/0xAI泡沫雷达_每日数据.xlsx
+++ b/data/0xAI泡沫雷达_每日数据.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVDA" sheetId="1" r:id="Re3986454fea2414c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态颜色规则" sheetId="2" r:id="R4981414e64534cd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="3" r:id="Rb06429f259b042c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archive" sheetId="1" r:id="Rc9ff60a0a2ac426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVDA" sheetId="2" r:id="R3d8ae89c4de64996"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="3" r:id="R0a7ca5fd59274c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="4" r:id="Rf010b4019e814367"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,11 +18,23 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-    <x:numFmt numFmtId="201" formatCode="0.00"/>
+    <x:numFmt numFmtId="201" formatCode="$0.00"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF475467"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -30,8 +43,65 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF344054"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF667085"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF344054"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFE60012"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFF97316"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFF97316"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -40,98 +110,314 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF111827"/>
+        <x:fgColor rgb="FF101828"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF111827"/>
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6941C6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4E5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF101828"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6941C6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="5">
     <x:border/>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFD1D5DB"/>
+        <x:color rgb="FF53389E"/>
       </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF53389E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF53389E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF53389E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF53389E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:right style="thin">
-        <x:color rgb="FFD1D5DB"/>
+        <x:color rgb="FF53389E"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFD1D5DB"/>
+        <x:color rgb="FF53389E"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFD1D5DB"/>
+        <x:color rgb="FF53389E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD0D5DD"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="88">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NVDA_DailyBubbleRadar" displayName="NVDA_DailyBubbleRadar" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="日期"/>
-    <x:tableColumn id="2" name="股票名称"/>
-    <x:tableColumn id="3" name="股票代码"/>
-    <x:tableColumn id="4" name="收盘价"/>
-    <x:tableColumn id="5" name="币种"/>
-    <x:tableColumn id="6" name="泡沫状态"/>
-    <x:tableColumn id="7" name="来源备注"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -329,66 +615,104 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="22.5" customHeight="1">
-      <x:c r="A1" s="11" t="str">
-        <x:v>日期</x:v>
-      </x:c>
-      <x:c r="B1" s="11" t="str">
-        <x:v>股票名称</x:v>
-      </x:c>
-      <x:c r="C1" s="11" t="str">
-        <x:v>股票代码</x:v>
-      </x:c>
-      <x:c r="D1" s="11" t="str">
-        <x:v>收盘价</x:v>
-      </x:c>
-      <x:c r="E1" s="11" t="str">
-        <x:v>币种</x:v>
-      </x:c>
-      <x:c r="F1" s="11" t="str">
-        <x:v>泡沫状态</x:v>
-      </x:c>
-      <x:c r="G1" s="11" t="str">
-        <x:v>来源备注</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="36" customHeight="1">
-      <x:c r="A2" s="12" t="n">
-        <x:v>46215</x:v>
-      </x:c>
-      <x:c r="B2" s="13" t="str">
-        <x:v>NVIDIA Corporation</x:v>
-      </x:c>
-      <x:c r="C2" s="13" t="str">
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>0xAI Bubble Radar | Historical Archive</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>All daily observations; append one row per U.S. trading day</x:v>
+      </x:c>
+      <x:c r="B2" s="8"/>
+      <x:c r="C2" s="8"/>
+      <x:c r="D2" s="8"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="17" t="str">
+        <x:v>Trading Date</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>Close (USD)</x:v>
+      </x:c>
+      <x:c r="D4" s="19" t="str">
+        <x:v>Bubble Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="39" t="n">
+        <x:v>46230</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
         <x:v>NVDA</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="n">
-        <x:v>210.96</x:v>
-      </x:c>
-      <x:c r="E2" s="13" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="F2" s="13" t="str">
-        <x:v>中性</x:v>
-      </x:c>
-      <x:c r="G2" s="13" t="str">
-        <x:v>TradingView 仪表盘截图，amazngxlaa 与 TradingView.com 共创，2026-07-12 16:40 UTC+8</x:v>
-      </x:c>
+      <x:c r="C5" s="41" t="n">
+        <x:v>196.51</x:v>
+      </x:c>
+      <x:c r="D5" s="44" t="str">
+        <x:v>NEUTRAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="39" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="B6" s="40" t="str">
+        <x:v>AAPL</x:v>
+      </x:c>
+      <x:c r="C6" s="41" t="n">
+        <x:v>340.08</x:v>
+      </x:c>
+      <x:c r="D6" s="53" t="str">
+        <x:v>EXTREME</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="60" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="B7" s="61" t="str">
+        <x:v>MSFT</x:v>
+      </x:c>
+      <x:c r="C7" s="62" t="n">
+        <x:v>390.54</x:v>
+      </x:c>
+      <x:c r="D7" s="65" t="str">
+        <x:v>ELEVATED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="34" t="str">
+        <x:v>Date = actual U.S. market trading day. Bubble status is informational, not investment advice.</x:v>
+      </x:c>
+      <x:c r="B9" s="34"/>
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A9:D9"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D500">
+      <x:formula1>"MINIMAL,LOW,NEUTRAL,ELEVATED,EXTREME"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c3fe05d769b4610"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -396,59 +720,75 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>泡沫状态</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>颜色</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="4" t="str">
-        <x:v>泡沫减减</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="str">
-        <x:v>绿色</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4" t="str">
-        <x:v>泡沫减</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="str">
-        <x:v>蓝色</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4" t="str">
-        <x:v>中性</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>灰色</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="4" t="str">
-        <x:v>泡沫加</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="str">
-        <x:v>橙色</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="4" t="str">
-        <x:v>泡沫加加</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="str">
-        <x:v>红色</x:v>
-      </x:c>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>0xAI Bubble Radar | NVDA</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>Historical bubble-status observations for NVDA</x:v>
+      </x:c>
+      <x:c r="B2" s="8"/>
+      <x:c r="C2" s="8"/>
+      <x:c r="D2" s="8"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="17" t="str">
+        <x:v>Trading Date</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>Close (USD)</x:v>
+      </x:c>
+      <x:c r="D4" s="19" t="str">
+        <x:v>Bubble Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="26" t="n">
+        <x:v>46230</x:v>
+      </x:c>
+      <x:c r="B5" s="27" t="str">
+        <x:v>NVDA</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="n">
+        <x:v>196.51</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>NEUTRAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="34" t="str">
+        <x:v>Date = actual U.S. market trading day. Bubble status is informational, not investment advice.</x:v>
+      </x:c>
+      <x:c r="B7" s="34"/>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A7:D7"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D500">
+      <x:formula1>"MINIMAL,LOW,NEUTRAL,ELEVATED,EXTREME"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -457,62 +797,152 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="22.5" customHeight="1">
-      <x:c r="A1" s="19" t="str">
-        <x:v>日期</x:v>
-      </x:c>
-      <x:c r="B1" s="19" t="str">
-        <x:v>股票名称</x:v>
-      </x:c>
-      <x:c r="C1" s="19" t="str">
-        <x:v>股票代码</x:v>
-      </x:c>
-      <x:c r="D1" s="19" t="str">
-        <x:v>收盘价</x:v>
-      </x:c>
-      <x:c r="E1" s="19" t="str">
-        <x:v>币种</x:v>
-      </x:c>
-      <x:c r="F1" s="19" t="str">
-        <x:v>泡沫状态</x:v>
-      </x:c>
-      <x:c r="G1" s="19" t="str">
-        <x:v>来源备注</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="31.5" customHeight="1">
-      <x:c r="A2" s="12" t="n">
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="69" t="str">
+        <x:v>0xAI Bubble Radar | AAPL</x:v>
+      </x:c>
+      <x:c r="B1" s="69"/>
+      <x:c r="C1" s="69"/>
+      <x:c r="D1" s="69"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="73" t="str">
+        <x:v>Historical bubble-status observations for AAPL</x:v>
+      </x:c>
+      <x:c r="B2" s="73"/>
+      <x:c r="C2" s="73"/>
+      <x:c r="D2" s="73"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="82" t="str">
+        <x:v>Trading Date</x:v>
+      </x:c>
+      <x:c r="B4" s="83" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="C4" s="83" t="str">
+        <x:v>Close (USD)</x:v>
+      </x:c>
+      <x:c r="D4" s="84" t="str">
+        <x:v>Bubble Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="39" t="n">
         <x:v>46231</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="str">
-        <x:v>Apple Inc.</x:v>
-      </x:c>
-      <x:c r="C2" s="13" t="str">
+      <x:c r="B5" s="40" t="str">
         <x:v>AAPL</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="n">
+      <x:c r="C5" s="41" t="n">
         <x:v>340.08</x:v>
       </x:c>
-      <x:c r="E2" s="13" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="F2" s="13" t="str">
+      <x:c r="D5" s="53" t="str">
         <x:v>EXTREME</x:v>
       </x:c>
-      <x:c r="G2" s="13" t="str">
-        <x:v>User-provided final 0xAI Bubble Radar card</x:v>
-      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="34" t="str">
+        <x:v>Date = actual U.S. market trading day. Bubble status is informational, not investment advice.</x:v>
+      </x:c>
+      <x:c r="B7" s="34"/>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A7:D7"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D500">
+      <x:formula1>"MINIMAL,LOW,NEUTRAL,ELEVATED,EXTREME"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="69" t="str">
+        <x:v>0xAI Bubble Radar | MSFT</x:v>
+      </x:c>
+      <x:c r="B1" s="69"/>
+      <x:c r="C1" s="69"/>
+      <x:c r="D1" s="69"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="73" t="str">
+        <x:v>Historical bubble-status observations for MSFT</x:v>
+      </x:c>
+      <x:c r="B2" s="73"/>
+      <x:c r="C2" s="73"/>
+      <x:c r="D2" s="73"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="82" t="str">
+        <x:v>Trading Date</x:v>
+      </x:c>
+      <x:c r="B4" s="83" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="C4" s="83" t="str">
+        <x:v>Close (USD)</x:v>
+      </x:c>
+      <x:c r="D4" s="84" t="str">
+        <x:v>Bubble Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="39" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>MSFT</x:v>
+      </x:c>
+      <x:c r="C5" s="41" t="n">
+        <x:v>390.54</x:v>
+      </x:c>
+      <x:c r="D5" s="87" t="str">
+        <x:v>ELEVATED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="34" t="str">
+        <x:v>Date = actual U.S. market trading day. Bubble status is informational, not investment advice.</x:v>
+      </x:c>
+      <x:c r="B7" s="34"/>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A7:D7"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D5:D500">
+      <x:formula1>"MINIMAL,LOW,NEUTRAL,ELEVATED,EXTREME"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>